--- a/data/trans_dic/P64D$particular_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P64D$particular_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,06; 72,74</t>
+          <t>38,42; 71,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41,62; 69,2</t>
+          <t>43,31; 70,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,37; 66,91</t>
+          <t>44,49; 67,35</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>67,72; 79,42</t>
+          <t>67,42; 79,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,27; 66,28</t>
+          <t>24,8; 66,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42,32; 70,95</t>
+          <t>43,92; 71,09</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,55; 81,24</t>
+          <t>73,5; 81,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,96; 69,58</t>
+          <t>60,96; 69,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,04; 75,08</t>
+          <t>69,22; 74,95</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>78,36; 94,88</t>
+          <t>78,53; 94,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,05; 73,87</t>
+          <t>62,02; 73,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,62; 88,5</t>
+          <t>72,85; 89,49</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,5; 76,03</t>
+          <t>66,43; 75,93</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,54; 59,66</t>
+          <t>49,04; 59,88</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61,1; 68,23</t>
+          <t>60,83; 68,5</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,53; 60,08</t>
+          <t>23,37; 62,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,46; 52,62</t>
+          <t>21,04; 52,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,84; 51,34</t>
+          <t>26,13; 50,06</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>74,16; 85,11</t>
+          <t>73,96; 84,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50,57; 64,29</t>
+          <t>50,31; 64,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65,66; 76,61</t>
+          <t>65,89; 75,8</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto)</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios en vehículo particular (automóvil, moto) (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36301; 65919</t>
+          <t>34818; 64537</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33815; 56217</t>
+          <t>35185; 57556</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76254; 114986</t>
+          <t>76452; 115747</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>237237; 278227</t>
+          <t>236192; 277518</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95384; 231798</t>
+          <t>86739; 232235</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>296295; 496693</t>
+          <t>307445; 497678</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>339768; 375304</t>
+          <t>339562; 376239</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>214085; 244375</t>
+          <t>214086; 244663</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>561435; 610531</t>
+          <t>562862; 609438</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>583863; 706915</t>
+          <t>585088; 703949</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>281030; 334552</t>
+          <t>280896; 333127</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>869965; 1060220</t>
+          <t>872736; 1072008</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>198940; 227423</t>
+          <t>198731; 227136</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>103109; 124183</t>
+          <t>102070; 124629</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>309950; 346123</t>
+          <t>308563; 347459</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3987; 10179</t>
+          <t>3959; 10627</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3632; 9340</t>
+          <t>3734; 9243</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>8963; 17813</t>
+          <t>9064; 17367</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1457763; 1673040</t>
+          <t>1453831; 1670403</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>738808; 939288</t>
+          <t>735063; 936876</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2249815; 2625071</t>
+          <t>2257817; 2597394</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P64D$particular_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P64D$particular_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>52,0%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>38,42; 71,22</t>
+          <t>33,32; 63,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>43,31; 70,85</t>
+          <t>39,92; 67,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44,49; 67,35</t>
+          <t>41,8; 62,63</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>67,07%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>67,42; 79,21</t>
+          <t>66,11; 77,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>24,8; 66,41</t>
+          <t>55,4; 66,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43,92; 71,09</t>
+          <t>63,05; 71,68</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>65,35%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>73,5; 81,44</t>
+          <t>71,8; 79,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,96; 69,66</t>
+          <t>60,02; 68,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69,22; 74,95</t>
+          <t>68,22; 73,75</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>66,82%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>72,01%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>78,53; 94,48</t>
+          <t>74,44; 81,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,02; 73,56</t>
+          <t>60,66; 67,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72,85; 89,49</t>
+          <t>69,25; 74,46</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>62,67%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,43; 75,93</t>
+          <t>64,11; 74,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>49,04; 59,88</t>
+          <t>47,68; 58,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60,83; 68,5</t>
+          <t>59,24; 66,53</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23,37; 62,72</t>
+          <t>24,35; 64,44</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>21,04; 52,07</t>
+          <t>23,14; 56,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26,13; 50,06</t>
+          <t>28,36; 53,59</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>48,81%</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>67,68%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>73,96; 84,98</t>
+          <t>70,66; 75,15</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>50,31; 64,13</t>
+          <t>58,52; 63,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>65,89; 75,8</t>
+          <t>66,02; 69,3</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51029</t>
+          <t>52600</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46419</t>
+          <t>49614</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97447</t>
+          <t>102214</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>34818; 64537</t>
+          <t>34930; 66726</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35185; 57556</t>
+          <t>36623; 62096</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>76452; 115747</t>
+          <t>82160; 123104</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>258590</t>
+          <t>284006</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>181059</t>
+          <t>192900</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>439649</t>
+          <t>476907</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>236192; 277518</t>
+          <t>261756; 305995</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86739; 232235</t>
+          <t>174582; 210496</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>307445; 497678</t>
+          <t>448344; 509677</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>357882</t>
+          <t>408355</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>229529</t>
+          <t>253953</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>587411</t>
+          <t>662308</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>339562; 376239</t>
+          <t>385208; 427829</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>214086; 244663</t>
+          <t>238284; 270360</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>562862; 609438</t>
+          <t>636813; 688494</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>643064</t>
+          <t>426416</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>302625</t>
+          <t>292663</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>945689</t>
+          <t>719079</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>585088; 703949</t>
+          <t>404635; 444088</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>280896; 333127</t>
+          <t>275989; 307534</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>872736; 1072008</t>
+          <t>691534; 743507</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>212979</t>
+          <t>227382</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>113956</t>
+          <t>123667</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>326935</t>
+          <t>351049</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>198731; 227136</t>
+          <t>209890; 243719</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>102070; 124629</t>
+          <t>110971; 135323</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>308563; 347459</t>
+          <t>331815; 372683</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>8361</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6222</t>
+          <t>7651</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13258</t>
+          <t>16012</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3959; 10627</t>
+          <t>4668; 12350</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3734; 9243</t>
+          <t>4563; 11074</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9064; 17367</t>
+          <t>11029; 20840</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1521,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1598</t>
+          <t>0; 1817</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1598</t>
+          <t>0; 1817</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>1531325</t>
+          <t>1408006</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>879809</t>
+          <t>920448</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2411135</t>
+          <t>2328455</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1453831; 1670403</t>
+          <t>1363077; 1449760</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>735063; 936876</t>
+          <t>884410; 953875</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2257817; 2597394</t>
+          <t>2271399; 2384275</t>
         </is>
       </c>
     </row>
